--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhonedcel_nolasco\Desktop\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B58054-5F2F-4DB0-99AB-4D8BF037DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78489E58-22B2-4CEB-A027-8D2DC520D501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
   <si>
     <t>HP 15</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Part Number</t>
+  </si>
+  <si>
+    <t>Promo DP</t>
   </si>
 </sst>
 </file>
@@ -13155,20 +13158,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
-  <dimension ref="B2:J23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:K23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.265625" customWidth="1"/>
+    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>63</v>
       </c>
@@ -13194,10 +13197,13 @@
         <v>57</v>
       </c>
       <c r="J2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
@@ -13222,14 +13228,15 @@
         <v>56990</v>
       </c>
       <c r="I3" s="2">
-        <f>H3*0.8</f>
-        <v>45592</v>
-      </c>
-      <c r="J3">
+        <f>H3*0.85</f>
+        <v>48441.5</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
@@ -13254,14 +13261,15 @@
         <v>62990</v>
       </c>
       <c r="I4" s="2">
-        <f t="shared" ref="I4:I23" si="0">H4*0.8</f>
-        <v>50392</v>
-      </c>
-      <c r="J4">
+        <f t="shared" ref="I4:I23" si="0">H4*0.85</f>
+        <v>53541.5</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4">
         <v>705</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
@@ -13287,13 +13295,14 @@
       </c>
       <c r="I5" s="2">
         <f t="shared" si="0"/>
-        <v>47192</v>
-      </c>
-      <c r="J5">
+        <v>50141.5</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
@@ -13319,13 +13328,17 @@
       </c>
       <c r="I6" s="2">
         <f t="shared" si="0"/>
+        <v>51841.5</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" ref="J6:J11" si="1">H6*0.8</f>
         <v>48792</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
@@ -13351,13 +13364,17 @@
       </c>
       <c r="I7" s="2">
         <f t="shared" si="0"/>
+        <v>51841.5</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="1"/>
         <v>48792</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
@@ -13383,13 +13400,17 @@
       </c>
       <c r="I8" s="2">
         <f t="shared" si="0"/>
+        <v>55241.5</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="1"/>
         <v>51992</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>875</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
@@ -13415,13 +13436,17 @@
       </c>
       <c r="I9" s="2">
         <f t="shared" si="0"/>
+        <v>73091.5</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="1"/>
         <v>68792</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>290</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
@@ -13447,13 +13472,17 @@
       </c>
       <c r="I10" s="2">
         <f t="shared" si="0"/>
+        <v>74791.5</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="1"/>
         <v>70392</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
@@ -13479,13 +13508,17 @@
       </c>
       <c r="I11" s="2">
         <f t="shared" si="0"/>
+        <v>68841.5</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="1"/>
         <v>64792</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
@@ -13511,13 +13544,14 @@
       </c>
       <c r="I12" s="2">
         <f t="shared" si="0"/>
-        <v>83192</v>
-      </c>
-      <c r="J12">
+        <v>88391.5</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12">
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
@@ -13543,13 +13577,14 @@
       </c>
       <c r="I13" s="2">
         <f t="shared" si="0"/>
-        <v>91192</v>
-      </c>
-      <c r="J13">
+        <v>96891.5</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
@@ -13575,13 +13610,14 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" si="0"/>
-        <v>111192</v>
-      </c>
-      <c r="J14">
+        <v>118141.5</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
@@ -13607,13 +13643,14 @@
       </c>
       <c r="I15" s="2">
         <f t="shared" si="0"/>
-        <v>127992</v>
-      </c>
-      <c r="J15">
+        <v>135991.5</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
@@ -13639,13 +13676,14 @@
       </c>
       <c r="I16" s="2">
         <f t="shared" si="0"/>
-        <v>81592</v>
-      </c>
-      <c r="J16">
+        <v>86691.5</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
@@ -13671,13 +13709,14 @@
       </c>
       <c r="I17" s="2">
         <f t="shared" si="0"/>
-        <v>90392</v>
-      </c>
-      <c r="J17">
+        <v>96041.5</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17">
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
@@ -13703,13 +13742,14 @@
       </c>
       <c r="I18" s="2">
         <f t="shared" si="0"/>
-        <v>98392</v>
-      </c>
-      <c r="J18">
+        <v>104541.5</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
@@ -13735,13 +13775,14 @@
       </c>
       <c r="I19" s="2">
         <f t="shared" si="0"/>
-        <v>135992</v>
-      </c>
-      <c r="J19">
+        <v>144491.5</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
@@ -13767,13 +13808,14 @@
       </c>
       <c r="I20" s="2">
         <f t="shared" si="0"/>
-        <v>85592</v>
-      </c>
-      <c r="J20">
+        <v>90941.5</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20">
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
@@ -13799,13 +13841,14 @@
       </c>
       <c r="I21" s="2">
         <f t="shared" si="0"/>
-        <v>87992</v>
-      </c>
-      <c r="J21">
+        <v>93491.5</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
@@ -13831,13 +13874,14 @@
       </c>
       <c r="I22" s="2">
         <f t="shared" si="0"/>
-        <v>127192</v>
-      </c>
-      <c r="J22">
+        <v>135141.5</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
@@ -13863,9 +13907,10 @@
       </c>
       <c r="I23" s="2">
         <f t="shared" si="0"/>
-        <v>46392</v>
-      </c>
-      <c r="J23" s="1">
+        <v>49291.5</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="1">
         <v>2267</v>
       </c>
     </row>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhonedcel_nolasco\Desktop\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78489E58-22B2-4CEB-A027-8D2DC520D501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB45EF43-BE68-4B20-B6D6-910DB3B03F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
   <si>
     <t>HP 15</t>
   </si>
@@ -208,9 +208,6 @@
     <t>SRP</t>
   </si>
   <si>
-    <t>Qty</t>
-  </si>
-  <si>
     <t>DP</t>
   </si>
   <si>
@@ -233,6 +230,12 @@
   </si>
   <si>
     <t>Promo DP</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Onhand</t>
   </si>
 </sst>
 </file>
@@ -279,9 +282,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -13173,10 +13175,10 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -13194,13 +13196,13 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" t="s">
         <v>64</v>
-      </c>
-      <c r="K2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -13208,7 +13210,7 @@
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>VLOOKUP(B3,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036894</v>
       </c>
@@ -13224,16 +13226,16 @@
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>56990</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <f>H3*0.85</f>
         <v>48441.5</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3">
-        <v>69</v>
+      <c r="J3" s="1"/>
+      <c r="K3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -13241,7 +13243,7 @@
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>VLOOKUP(B4,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036895</v>
       </c>
@@ -13257,16 +13259,16 @@
       <c r="G4" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>62990</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <f t="shared" ref="I4:I23" si="0">H4*0.85</f>
         <v>53541.5</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4">
-        <v>705</v>
+      <c r="J4" s="1"/>
+      <c r="K4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -13274,7 +13276,7 @@
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>VLOOKUP(B5,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036897</v>
       </c>
@@ -13290,16 +13292,16 @@
       <c r="G5" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>58990</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <f t="shared" si="0"/>
         <v>50141.5</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5">
-        <v>150</v>
+      <c r="J5" s="1"/>
+      <c r="K5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -13307,7 +13309,7 @@
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>VLOOKUP(B6,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036898</v>
       </c>
@@ -13315,7 +13317,7 @@
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -13323,19 +13325,19 @@
       <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>60990</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <f t="shared" si="0"/>
         <v>51841.5</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <f t="shared" ref="J6:J11" si="1">H6*0.8</f>
         <v>48792</v>
       </c>
-      <c r="K6">
-        <v>250</v>
+      <c r="K6" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -13343,7 +13345,7 @@
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>VLOOKUP(B7,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036899</v>
       </c>
@@ -13351,7 +13353,7 @@
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -13359,19 +13361,19 @@
       <c r="G7" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>60990</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <f t="shared" si="0"/>
         <v>51841.5</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <f t="shared" si="1"/>
         <v>48792</v>
       </c>
-      <c r="K7">
-        <v>250</v>
+      <c r="K7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -13379,7 +13381,7 @@
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>VLOOKUP(B8,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036900</v>
       </c>
@@ -13387,7 +13389,7 @@
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -13395,19 +13397,19 @@
       <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>64990</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
         <v>55241.5</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <f t="shared" si="1"/>
         <v>51992</v>
       </c>
-      <c r="K8">
-        <v>875</v>
+      <c r="K8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
@@ -13415,7 +13417,7 @@
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>VLOOKUP(B9,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036903</v>
       </c>
@@ -13423,7 +13425,7 @@
         <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -13431,19 +13433,19 @@
       <c r="G9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>85990</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <f t="shared" si="0"/>
         <v>73091.5</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <f t="shared" si="1"/>
         <v>68792</v>
       </c>
-      <c r="K9">
-        <v>290</v>
+      <c r="K9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
@@ -13451,7 +13453,7 @@
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>VLOOKUP(B10,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036904</v>
       </c>
@@ -13459,7 +13461,7 @@
         <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -13467,19 +13469,19 @@
       <c r="G10" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>87990</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <f t="shared" si="0"/>
         <v>74791.5</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <f t="shared" si="1"/>
         <v>70392</v>
       </c>
-      <c r="K10">
-        <v>196</v>
+      <c r="K10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
@@ -13487,7 +13489,7 @@
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>VLOOKUP(B11,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036907</v>
       </c>
@@ -13495,7 +13497,7 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
@@ -13503,19 +13505,19 @@
       <c r="G11" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>80990</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <f t="shared" si="0"/>
         <v>68841.5</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <f t="shared" si="1"/>
         <v>64792</v>
       </c>
-      <c r="K11">
-        <v>170</v>
+      <c r="K11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
@@ -13523,7 +13525,7 @@
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>VLOOKUP(B12,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036914</v>
       </c>
@@ -13531,7 +13533,7 @@
         <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -13539,16 +13541,16 @@
       <c r="G12" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>103990</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <f t="shared" si="0"/>
         <v>88391.5</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12">
-        <v>152</v>
+      <c r="J12" s="1"/>
+      <c r="K12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
@@ -13556,7 +13558,7 @@
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>VLOOKUP(B13,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036915</v>
       </c>
@@ -13564,7 +13566,7 @@
         <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -13572,16 +13574,16 @@
       <c r="G13" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>113990</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <f t="shared" si="0"/>
         <v>96891.5</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13">
-        <v>50</v>
+      <c r="J13" s="1"/>
+      <c r="K13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -13589,7 +13591,7 @@
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>VLOOKUP(B14,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036916</v>
       </c>
@@ -13597,7 +13599,7 @@
         <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>23</v>
@@ -13605,16 +13607,16 @@
       <c r="G14" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>138990</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
         <f t="shared" si="0"/>
         <v>118141.5</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14">
-        <v>10</v>
+      <c r="J14" s="1"/>
+      <c r="K14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
@@ -13622,7 +13624,7 @@
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>VLOOKUP(B15,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036917</v>
       </c>
@@ -13630,7 +13632,7 @@
         <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -13638,16 +13640,16 @@
       <c r="G15" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>159990</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <f t="shared" si="0"/>
         <v>135991.5</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15">
-        <v>9</v>
+      <c r="J15" s="1"/>
+      <c r="K15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
@@ -13655,7 +13657,7 @@
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>VLOOKUP(B16,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036919</v>
       </c>
@@ -13663,7 +13665,7 @@
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -13671,16 +13673,16 @@
       <c r="G16" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>101990</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <f t="shared" si="0"/>
         <v>86691.5</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16">
-        <v>15</v>
+      <c r="J16" s="1"/>
+      <c r="K16" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -13688,7 +13690,7 @@
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>VLOOKUP(B17,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036922</v>
       </c>
@@ -13696,7 +13698,7 @@
         <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
@@ -13704,16 +13706,16 @@
       <c r="G17" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>112990</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <f t="shared" si="0"/>
         <v>96041.5</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17">
-        <v>236</v>
+      <c r="J17" s="1"/>
+      <c r="K17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -13721,7 +13723,7 @@
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>VLOOKUP(B18,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036923</v>
       </c>
@@ -13729,7 +13731,7 @@
         <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
         <v>31</v>
@@ -13737,16 +13739,16 @@
       <c r="G18" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>122990</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
         <f t="shared" si="0"/>
         <v>104541.5</v>
       </c>
-      <c r="J18" s="2"/>
-      <c r="K18">
-        <v>95</v>
+      <c r="J18" s="1"/>
+      <c r="K18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -13754,7 +13756,7 @@
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>VLOOKUP(B19,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036924</v>
       </c>
@@ -13762,7 +13764,7 @@
         <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
@@ -13770,16 +13772,16 @@
       <c r="G19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>169990</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
         <f t="shared" si="0"/>
         <v>144491.5</v>
       </c>
-      <c r="J19" s="2"/>
-      <c r="K19">
-        <v>5</v>
+      <c r="J19" s="1"/>
+      <c r="K19" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -13787,7 +13789,7 @@
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <f>VLOOKUP(B20,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036925</v>
       </c>
@@ -13795,7 +13797,7 @@
         <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
         <v>35</v>
@@ -13803,16 +13805,16 @@
       <c r="G20" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>106990</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="1">
         <f t="shared" si="0"/>
         <v>90941.5</v>
       </c>
-      <c r="J20" s="2"/>
-      <c r="K20">
-        <v>249</v>
+      <c r="J20" s="1"/>
+      <c r="K20" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -13820,7 +13822,7 @@
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <f>VLOOKUP(B21,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036926</v>
       </c>
@@ -13828,7 +13830,7 @@
         <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
         <v>37</v>
@@ -13836,16 +13838,16 @@
       <c r="G21" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>109990</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="1">
         <f t="shared" si="0"/>
         <v>93491.5</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21">
-        <v>50</v>
+      <c r="J21" s="1"/>
+      <c r="K21" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
@@ -13853,7 +13855,7 @@
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <f>VLOOKUP(B22,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036927</v>
       </c>
@@ -13861,7 +13863,7 @@
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -13869,16 +13871,16 @@
       <c r="G22" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>158990</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
         <f t="shared" si="0"/>
         <v>135141.5</v>
       </c>
-      <c r="J22" s="2"/>
-      <c r="K22">
-        <v>10</v>
+      <c r="J22" s="1"/>
+      <c r="K22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -13886,7 +13888,7 @@
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <f>VLOOKUP(B23,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
         <v>432115036971</v>
       </c>
@@ -13902,16 +13904,16 @@
       <c r="G23" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>57990</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="1">
         <f t="shared" si="0"/>
         <v>49291.5</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="1">
-        <v>2267</v>
+      <c r="J23" s="1"/>
+      <c r="K23" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhonedcel_nolasco\Desktop\Test Pilot - HP Pricelist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB45EF43-BE68-4B20-B6D6-910DB3B03F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6122953-5906-4580-949E-08F912AFDDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
+    <workbookView xWindow="3083" yWindow="1238" windowWidth="16200" windowHeight="9307" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="126">
   <si>
     <t>HP 15</t>
   </si>
@@ -237,6 +237,186 @@
   <si>
     <t>Onhand</t>
   </si>
+  <si>
+    <t>E47WNPA</t>
+  </si>
+  <si>
+    <t>E47WPPA</t>
+  </si>
+  <si>
+    <t>E2HE2PA</t>
+  </si>
+  <si>
+    <t>E2HE3PA</t>
+  </si>
+  <si>
+    <t>E4PN6PA</t>
+  </si>
+  <si>
+    <t>E6GG0PA</t>
+  </si>
+  <si>
+    <t>E6GG2PA</t>
+  </si>
+  <si>
+    <t>E47WMPA</t>
+  </si>
+  <si>
+    <t>E6RZ4PA</t>
+  </si>
+  <si>
+    <t>E6RZ5PA</t>
+  </si>
+  <si>
+    <t>E6GG8PA</t>
+  </si>
+  <si>
+    <t>E47WSPA</t>
+  </si>
+  <si>
+    <t>E6GG9PA</t>
+  </si>
+  <si>
+    <t>E2HE0PA</t>
+  </si>
+  <si>
+    <t>E2HE1PA</t>
+  </si>
+  <si>
+    <t>E5MC6PA</t>
+  </si>
+  <si>
+    <t>E5MC7PA</t>
+  </si>
+  <si>
+    <t>Abe-I 26C1</t>
+  </si>
+  <si>
+    <t>Abe-A 26C1</t>
+  </si>
+  <si>
+    <t>Bantie-I 26C1</t>
+  </si>
+  <si>
+    <t>Bantie-A 26C1</t>
+  </si>
+  <si>
+    <t>Agusta 26C1</t>
+  </si>
+  <si>
+    <t>Truevalue</t>
+  </si>
+  <si>
+    <t>HP Laptop 15-fc0289AU</t>
+  </si>
+  <si>
+    <t>HP Laptop 15-fc0523AU</t>
+  </si>
+  <si>
+    <t>HP Laptop 15-fd1655TU</t>
+  </si>
+  <si>
+    <t>HP Laptop 15-fd1656TU</t>
+  </si>
+  <si>
+    <t>HP Laptop 15-fc0998AU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 AI PC 14-ht0270TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 AI PC 14-ht0271TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 14-hy0100AU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 16-bu0397TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 16-bu0398TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 16-by0121AU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 16-bu0384TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 16-bu0393TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 7 NG AI PC 14-hg0079TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook 7 NG AI PC 14-hg0080TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook X Flip NG AI PC 14-fm0206TU</t>
+  </si>
+  <si>
+    <t>HP OmniBook X Flip NG AI PC 14-fm0208TU</t>
+  </si>
+  <si>
+    <t>HP Laptop Clamshell | Otto 23C1 | Ryzen 5-7520U (Copilot) | 8GB 5500 LPDDR5 on-board | 512GB PCIe Value | AMD Radeon Graphics | 15.6 FHD (1920x1080) AG ultraslim SVA 250 nits Narrow Border  | Natural Silver (FF+) - 720p TNR PVCY ST | 45 Watt (Copilot) | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP Laptop Clamshell | Otto 23C1 | Ryzen 5-7520U (Copilot) | 16GB 5500 LPDDR5 on-board | 512GB PCIe Value | AMD Radeon Graphics | 15.6 FHD (1920x1080) AG ultraslim SVA 250 nits Narrow Border | Natural Silver (FF+) - 720p TNR PVCY ST | 45 Watt (Copilot) | 2-2-2| HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP Laptop Clamshell | Sebastian 24C1 | Core 5-120U (Copilot) | 8GB DDR4 1DM 3200 | 512GB PCIe value | Intel Graphics | 15.6 FHD (1920x1080) AG SVA 250 nits Narrow border ultraslim  | Natural Silver (FF+) - 1080p TNR PVCY ST | 45 Watt (Copilot) |2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC  |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP Laptop Clamshell | Sebastian 24C1 | Core 5-120U (Copilot) | 16GB DDR4 2DM 3200 | 512GB PCIe value | Intel Graphics | 15.6 FHD (1920x1080) AG SVA 250 nits Narrow border ultraslim | OST W11H6 PLS SL APACPPP | Natural Silver (FF+) - 1080p TNR PVCY ST | 45 Watt (Copilot) | WARR 1/1/0 A/P | HP 2y 3d Onsite Bundle Opp NB SVC</t>
+  </si>
+  <si>
+    <t>HP Laptop Clamshell | Otto 23C1 | Ryzen 7-7730U (Copilot) | 8GB DDR4 1DM 3200 | 512GB PCIe Value | AMD Radeon Graphics | 15.6 FHD (1920x1080) AG ultraslim SVA 250 nits Narrow Border  | Natural Silver (FF+) - 720p TNR PVCY ST | 45 Watt (Copilot) |2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 AI PC Clamshell | Abe-I 26C1 | Core 3 304 (5C) 15 NPU TOPs | 8GB DDR5 1DM 5600 | 512GB PCIe Gen4 Value | Intel Graphics | 14.0 2K (1920x1200) Antiglare IPS Low Power 300 nits | Glacier Silver DF+ - 1080p TNR | 45 Watt USB-C GaN |2-2-2| HP 2y 3d Onsite Bundle Opp NB SVC  |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 AI PC Clamshell | Abe-I 26C1 | Core 3 304 (5C) 15 NPU TOPs | 8GB DDR5 1DM 5600 | 512GB PCIe Gen4 Value | Intel Graphics | 14.0 2K (1920x1200) Antiglare IPS Low Power 300 nits  | Starlit Blue DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Abe-A 26C1 | Ryzen 5 130 (6C) | 8GB DDR5 1DM 4800 | 512GB PCIe Gen4 Value | AMD Radeon 660M Graphics | 14.0 2K (1920x1200) Antiglare IPS Low Power 300 nits | Mica Silver DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Bantie-I 26C1 | Core 5 315 (6C) 15 NPU TOPs | 16GB LPDDR5X 7467 on-board | 512GB PCIe Gen4 Value | Intel Graphics | 16.0 2K (1920x1200) Antiglare IPS 300 nits | OST W11H6 PLS SL APACPPP | Glacier Silver DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Bantie-I 26C1 | Core 5 315 (6C) 15 NPU TOPs | 16GB LPDDR5X 7467 on-board | 512GB PCIe Gen4 Value | Intel Graphics | 16.0 2K (1920x1200) Antiglare IPS 300 nits | Starlit Blue DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Bantie-A 26C1 | Ryzen 5 130 (6C) | 16GB DDR5 1DM 4800 | 512GB PCIe Gen4 Value | AMD Radeon 660M Graphics | 16.0 2K (1920x1200) Antiglare IPS 300 nits | Glacier Silver DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Bantie-I 26C1 | Core 7 350 (6C) 17 NPU TOPs | 16GB DDR5 1DM 5600 | 512GB PCIe Gen4 Value | Intel Graphics | 16.0 2K (1920x1200) Antiglare IPS 300 nits | Glacier Silver DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 3 Clamshell | Bantie-I 26C1 | Core 7 350 (6C) 17 NPU TOPs | 16GB DDR5 1DM 5600 | 512GB PCIe Gen4 Value | Intel Graphics | 16.0 2K (1920x1200) Antiglare IPS 300 nits  | Starlit Blue DF+ - 1080p TNR | 45 Watt USB-C GaN | 2-2-2 | HP 2y 3d Onsite Bundle Opp NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 7 NG AI PC Clamshell | Agusta 26C1 | Ultra X7 358H (16C) 50 NPU TOPs | 32GB LPDDR5X 8533 on-board | 512GB PCIe Gen4 Value | Intel Arc Pro B390 | 14.0 2K (1920x1200) OLED Brightview Low Blue Light 300 nits | Meteor Silver - 5MP IR TNR | 100 Watt USB-C Wall-Mount GaN | 2-2-2 | HP 2y 3d Onsite Bundle Medium NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook 7 NG AI PC Clamshell | Agusta 26C1 | Ultra X7 358H (16C) 50 NPU TOPs | 32GB LPDDR5X 8533 on-board | 512GB PCIe Gen4 Value | Intel Arc Pro B390 | 14.0 2K (1920x1200) OLED Brightview Low Blue Light 300 nits  | Powder Pink - 5MP IR TNR | 100 Watt USB-C Wall-Mount GaN | 2-2-2 | HP 2y 3d Onsite Bundle Medium NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook X Flip NG AI PC x360 | Cadet 25C1 | Ultra 7-256V (8C) 47 NPU TOPs | 16GB LPDDR5X 8533 on-board | 512GB PCIe Gen4 Value | Intel Arc 140V GPU | Touch/14.0 2K (1920x1200) IPS 400 nits | Atmospheric Blue AI logo - 5MP IR PVCY ST | 65 Watt USB C | 2-2-2 | HP 2y 3d Onsite Bundle Medium NB SVC |Win 11 Home | MS Office Home 2024 Philippines + 1yr M365 Basic</t>
+  </si>
+  <si>
+    <t>HP OmniBook X Flip NG AI PC x360 | Cadet 25C1 | Ultra 7-256V (8C) 47 NPU TOPs | 16GB LPDDR5X 8533 on-board | 512GB PCIe Gen4 Value | Intel Arc 140V GPU | Touch/14.0 2K (1920x1200) IPS 400 nits | OST W11H6 NG PRE SL APACPPP | Meteor Silver AI logo - 5MP IR PVCY ST | 65 Watt USB C | 2-2-2 | HP 2y 3d Onsite Bundle Medium NB SVC</t>
+  </si>
+  <si>
+    <t>Omnibook 7</t>
+  </si>
+  <si>
+    <t>Incoming</t>
+  </si>
+  <si>
+    <t>Order Basis</t>
+  </si>
 </sst>
 </file>
 
@@ -245,7 +425,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,16 +440,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -277,18 +482,112 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma 2 3" xfId="2" xr:uid="{2BCE3A47-9942-4B9C-8662-0B6C23B0585C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -694,13 +993,12 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ZMATINFO NB - 0924"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="4">
           <cell r="N4" t="str">
             <v>Ext. Description 2</v>
@@ -13160,20 +13458,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
-  <dimension ref="B2:K23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:K40"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -13205,7 +13503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
@@ -13238,7 +13536,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
@@ -13263,7 +13561,7 @@
         <v>62990</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" ref="I4:I23" si="0">H4*0.85</f>
+        <f t="shared" ref="I4:I40" si="0">H4*0.85</f>
         <v>53541.5</v>
       </c>
       <c r="J4" s="1"/>
@@ -13271,7 +13569,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
@@ -13304,7 +13602,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
@@ -13340,7 +13638,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
@@ -13376,7 +13674,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
@@ -13412,7 +13710,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
@@ -13448,7 +13746,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
@@ -13484,7 +13782,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
@@ -13520,7 +13818,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
@@ -13553,7 +13851,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
@@ -13586,7 +13884,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
@@ -13619,7 +13917,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
@@ -13652,7 +13950,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
@@ -13685,7 +13983,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
@@ -13718,7 +14016,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
@@ -13751,7 +14049,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
@@ -13784,7 +14082,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
@@ -13817,7 +14115,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
@@ -13850,7 +14148,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
@@ -13883,7 +14181,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
@@ -13913,10 +14211,540 @@
       </c>
       <c r="J23" s="1"/>
       <c r="K23" t="s">
-        <v>65</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2">
+        <f>VLOOKUP(B24,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037064</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="14">
+        <v>64990</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+        <v>55241.5</v>
+      </c>
+      <c r="K24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="2">
+        <f>VLOOKUP(B25,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037065</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="14">
+        <v>77990</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+        <v>66291.5</v>
+      </c>
+      <c r="K25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="2">
+        <f>VLOOKUP(B26,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037067</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" s="15">
+        <v>66990</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
+        <v>56941.5</v>
+      </c>
+      <c r="K26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="2">
+        <f>VLOOKUP(B27,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037139</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="16">
+        <v>78990</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+        <v>67141.5</v>
+      </c>
+      <c r="K27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="2">
+        <f>VLOOKUP(B28,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037068</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="14">
+        <v>67990</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="0"/>
+        <v>57791.5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2">
+        <f>VLOOKUP(B29,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037086</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="15">
+        <v>63990</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="0"/>
+        <v>54391.5</v>
+      </c>
+      <c r="K29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2">
+        <f>VLOOKUP(B30,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037087</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="15">
+        <v>63990</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="0"/>
+        <v>54391.5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="2">
+        <f>VLOOKUP(B31,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037097</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="14">
+        <v>69990</v>
+      </c>
+      <c r="I31" s="1">
+        <f t="shared" si="0"/>
+        <v>59491.5</v>
+      </c>
+      <c r="K31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="2">
+        <f>VLOOKUP(B32,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037098</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="15">
+        <v>79990</v>
+      </c>
+      <c r="I32" s="1">
+        <f t="shared" si="0"/>
+        <v>67991.5</v>
+      </c>
+      <c r="K32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="2">
+        <f>VLOOKUP(B33,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037088</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="15">
+        <v>79990</v>
+      </c>
+      <c r="I33" s="1">
+        <f t="shared" si="0"/>
+        <v>67991.5</v>
+      </c>
+      <c r="K33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="2">
+        <f>VLOOKUP(B34,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037089</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="14">
+        <v>82990</v>
+      </c>
+      <c r="I34" s="1">
+        <f t="shared" si="0"/>
+        <v>70541.5</v>
+      </c>
+      <c r="K34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="2">
+        <f>VLOOKUP(B35,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037090</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="14">
+        <v>95990</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" si="0"/>
+        <v>81591.5</v>
+      </c>
+      <c r="K35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2">
+        <f>VLOOKUP(B36,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037091</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="14">
+        <v>95990</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="0"/>
+        <v>81591.5</v>
+      </c>
+      <c r="K36" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="2">
+        <f>VLOOKUP(B37,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037092</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="15">
+        <v>149990</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="0"/>
+        <v>127491.5</v>
+      </c>
+      <c r="K37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="2">
+        <f>VLOOKUP(B38,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037093</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H38" s="15">
+        <v>149990</v>
+      </c>
+      <c r="I38" s="1">
+        <f t="shared" si="0"/>
+        <v>127491.5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="2">
+        <f>VLOOKUP(B39,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037094</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="14">
+        <v>98990</v>
+      </c>
+      <c r="I39" s="1">
+        <f t="shared" si="0"/>
+        <v>84141.5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="2">
+        <f>VLOOKUP(B40,'[2]ZMATINFO NB - 0924'!$N:$R,4,0)</f>
+        <v>432115037095</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="14">
+        <v>98990</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="0"/>
+        <v>84141.5</v>
+      </c>
+      <c r="K40" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Will be populated a few days after product is frozen" sqref="B39:B40 B35 B26:B28" xr:uid="{22BA7B52-23EF-4AFC-A745-BE66CB2ABC6E}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6122953-5906-4580-949E-08F912AFDDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBD77B9-FC86-4139-9DF1-071184053830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3083" yWindow="1238" windowWidth="16200" windowHeight="9307" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="130">
   <si>
     <t>HP 15</t>
   </si>
@@ -417,6 +417,18 @@
   <si>
     <t>Order Basis</t>
   </si>
+  <si>
+    <t>Promo SRP</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Maximum 50 units only until Oct 31, 2026</t>
+  </si>
+  <si>
+    <t>Maximum 350 units only until Oct 31, 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -13458,20 +13470,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
-  <dimension ref="B2:K40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:M40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.265625" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -13497,13 +13510,19 @@
         <v>56</v>
       </c>
       <c r="J2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" t="s">
         <v>63</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>64</v>
       </c>
+      <c r="M2" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
@@ -13532,11 +13551,12 @@
         <v>48441.5</v>
       </c>
       <c r="J3" s="1"/>
-      <c r="K3" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
@@ -13565,11 +13585,12 @@
         <v>53541.5</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" t="s">
+      <c r="K4" s="1"/>
+      <c r="L4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
@@ -13598,11 +13619,12 @@
         <v>50141.5</v>
       </c>
       <c r="J5" s="1"/>
-      <c r="K5" t="s">
+      <c r="K5" s="1"/>
+      <c r="L5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
@@ -13631,14 +13653,20 @@
         <v>51841.5</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" ref="J6:J11" si="1">H6*0.8</f>
-        <v>48792</v>
-      </c>
-      <c r="K6" t="s">
+        <v>44990</v>
+      </c>
+      <c r="K6" s="1">
+        <f>J6*0.85</f>
+        <v>38241.5</v>
+      </c>
+      <c r="L6" t="s">
         <v>65</v>
       </c>
+      <c r="M6" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
@@ -13667,14 +13695,20 @@
         <v>51841.5</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="1"/>
-        <v>48792</v>
-      </c>
-      <c r="K7" t="s">
+        <v>44990</v>
+      </c>
+      <c r="K7" s="1">
+        <f>J7*0.85</f>
+        <v>38241.5</v>
+      </c>
+      <c r="L7" t="s">
         <v>65</v>
       </c>
+      <c r="M7" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
@@ -13703,14 +13737,20 @@
         <v>55241.5</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="1"/>
-        <v>51992</v>
-      </c>
-      <c r="K8" t="s">
+        <v>60990</v>
+      </c>
+      <c r="K8" s="1">
+        <f>J8*0.85</f>
+        <v>51841.5</v>
+      </c>
+      <c r="L8" t="s">
         <v>65</v>
       </c>
+      <c r="M8" t="s">
+        <v>129</v>
+      </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
@@ -13738,15 +13778,16 @@
         <f t="shared" si="0"/>
         <v>73091.5</v>
       </c>
-      <c r="J9" s="1">
-        <f t="shared" si="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <f t="shared" ref="K6:K11" si="1">H9*0.8</f>
         <v>68792</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
@@ -13774,15 +13815,16 @@
         <f t="shared" si="0"/>
         <v>74791.5</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
         <f t="shared" si="1"/>
         <v>70392</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
@@ -13810,15 +13852,16 @@
         <f t="shared" si="0"/>
         <v>68841.5</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
         <f t="shared" si="1"/>
         <v>64792</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
@@ -13847,11 +13890,12 @@
         <v>88391.5</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
@@ -13880,11 +13924,12 @@
         <v>96891.5</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
@@ -13913,11 +13958,12 @@
         <v>118141.5</v>
       </c>
       <c r="J14" s="1"/>
-      <c r="K14" t="s">
+      <c r="K14" s="1"/>
+      <c r="L14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
@@ -13946,11 +13992,12 @@
         <v>135991.5</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" t="s">
+      <c r="K15" s="1"/>
+      <c r="L15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
@@ -13979,11 +14026,12 @@
         <v>86691.5</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
@@ -14012,11 +14060,12 @@
         <v>96041.5</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" t="s">
+      <c r="K17" s="1"/>
+      <c r="L17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
@@ -14045,11 +14094,12 @@
         <v>104541.5</v>
       </c>
       <c r="J18" s="1"/>
-      <c r="K18" t="s">
+      <c r="K18" s="1"/>
+      <c r="L18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
@@ -14078,11 +14128,12 @@
         <v>144491.5</v>
       </c>
       <c r="J19" s="1"/>
-      <c r="K19" t="s">
+      <c r="K19" s="1"/>
+      <c r="L19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
@@ -14111,11 +14162,12 @@
         <v>90941.5</v>
       </c>
       <c r="J20" s="1"/>
-      <c r="K20" t="s">
+      <c r="K20" s="1"/>
+      <c r="L20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
@@ -14144,11 +14196,12 @@
         <v>93491.5</v>
       </c>
       <c r="J21" s="1"/>
-      <c r="K21" t="s">
+      <c r="K21" s="1"/>
+      <c r="L21" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
@@ -14177,11 +14230,12 @@
         <v>135141.5</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="K22" t="s">
+      <c r="K22" s="1"/>
+      <c r="L22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
@@ -14210,11 +14264,12 @@
         <v>49291.5</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="K23" t="s">
+      <c r="K23" s="1"/>
+      <c r="L23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>66</v>
       </c>
@@ -14241,11 +14296,12 @@
         <f t="shared" si="0"/>
         <v>55241.5</v>
       </c>
-      <c r="K24" t="s">
+      <c r="J24" s="1"/>
+      <c r="L24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>67</v>
       </c>
@@ -14272,11 +14328,12 @@
         <f t="shared" si="0"/>
         <v>66291.5</v>
       </c>
-      <c r="K25" t="s">
+      <c r="J25" s="1"/>
+      <c r="L25" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
@@ -14303,11 +14360,12 @@
         <f t="shared" si="0"/>
         <v>56941.5</v>
       </c>
-      <c r="K26" t="s">
+      <c r="J26" s="1"/>
+      <c r="L26" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
@@ -14334,11 +14392,12 @@
         <f t="shared" si="0"/>
         <v>67141.5</v>
       </c>
-      <c r="K27" t="s">
+      <c r="J27" s="1"/>
+      <c r="L27" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>70</v>
       </c>
@@ -14365,11 +14424,12 @@
         <f t="shared" si="0"/>
         <v>57791.5</v>
       </c>
-      <c r="K28" t="s">
+      <c r="J28" s="1"/>
+      <c r="L28" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>71</v>
       </c>
@@ -14396,11 +14456,12 @@
         <f t="shared" si="0"/>
         <v>54391.5</v>
       </c>
-      <c r="K29" t="s">
+      <c r="J29" s="1"/>
+      <c r="L29" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>72</v>
       </c>
@@ -14427,11 +14488,12 @@
         <f t="shared" si="0"/>
         <v>54391.5</v>
       </c>
-      <c r="K30" t="s">
+      <c r="J30" s="1"/>
+      <c r="L30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>73</v>
       </c>
@@ -14458,11 +14520,12 @@
         <f t="shared" si="0"/>
         <v>59491.5</v>
       </c>
-      <c r="K31" t="s">
+      <c r="J31" s="1"/>
+      <c r="L31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>74</v>
       </c>
@@ -14489,11 +14552,12 @@
         <f t="shared" si="0"/>
         <v>67991.5</v>
       </c>
-      <c r="K32" t="s">
+      <c r="J32" s="1"/>
+      <c r="L32" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>75</v>
       </c>
@@ -14520,11 +14584,12 @@
         <f t="shared" si="0"/>
         <v>67991.5</v>
       </c>
-      <c r="K33" t="s">
+      <c r="J33" s="1"/>
+      <c r="L33" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>76</v>
       </c>
@@ -14551,11 +14616,12 @@
         <f t="shared" si="0"/>
         <v>70541.5</v>
       </c>
-      <c r="K34" t="s">
+      <c r="J34" s="1"/>
+      <c r="L34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
@@ -14582,11 +14648,12 @@
         <f t="shared" si="0"/>
         <v>81591.5</v>
       </c>
-      <c r="K35" t="s">
+      <c r="J35" s="1"/>
+      <c r="L35" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>78</v>
       </c>
@@ -14613,11 +14680,12 @@
         <f t="shared" si="0"/>
         <v>81591.5</v>
       </c>
-      <c r="K36" t="s">
+      <c r="J36" s="1"/>
+      <c r="L36" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>79</v>
       </c>
@@ -14644,11 +14712,12 @@
         <f t="shared" si="0"/>
         <v>127491.5</v>
       </c>
-      <c r="K37" t="s">
+      <c r="J37" s="1"/>
+      <c r="L37" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
@@ -14675,11 +14744,12 @@
         <f t="shared" si="0"/>
         <v>127491.5</v>
       </c>
-      <c r="K38" t="s">
+      <c r="J38" s="1"/>
+      <c r="L38" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>81</v>
       </c>
@@ -14706,11 +14776,12 @@
         <f t="shared" si="0"/>
         <v>84141.5</v>
       </c>
-      <c r="K39" t="s">
+      <c r="J39" s="1"/>
+      <c r="L39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>82</v>
       </c>
@@ -14737,7 +14808,8 @@
         <f t="shared" si="0"/>
         <v>84141.5</v>
       </c>
-      <c r="K40" t="s">
+      <c r="J40" s="1"/>
+      <c r="L40" t="s">
         <v>124</v>
       </c>
     </row>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBD77B9-FC86-4139-9DF1-071184053830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7392DCC3-0558-4706-A810-07178E3ABDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="134">
   <si>
     <t>HP 15</t>
   </si>
@@ -429,6 +429,18 @@
   <si>
     <t>Maximum 350 units only until Oct 31, 2026</t>
   </si>
+  <si>
+    <t>Probook</t>
+  </si>
+  <si>
+    <t>U5-225U 8GB 256GB W11 HOME 1/1/1 WS BUS</t>
+  </si>
+  <si>
+    <t>HP Probook 4 G1I 14 AI Commercial On Retail</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
 </sst>
 </file>
 
@@ -13470,7 +13482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
-  <dimension ref="B2:M40"/>
+  <dimension ref="B2:M41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -13780,7 +13792,7 @@
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
-        <f t="shared" ref="K6:K11" si="1">H9*0.8</f>
+        <f t="shared" ref="K9:K11" si="1">H9*0.8</f>
         <v>68792</v>
       </c>
       <c r="L9" t="s">
@@ -14811,6 +14823,40 @@
       <c r="J40" s="1"/>
       <c r="L40" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BQ5B1PT</t>
+        </is>
+      </c>
+      <c r="C41" s="2">
+        <v>432115037006</v>
+      </c>
+      <c r="E41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" s="1">
+        <v>77990</v>
+      </c>
+      <c r="I41" s="1">
+        <v>61706</v>
+      </c>
+      <c r="J41" s="1">
+        <v>73990</v>
+      </c>
+      <c r="K41" s="1">
+        <v>59000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7392DCC3-0558-4706-A810-07178E3ABDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28D1CD0-2C76-4ADD-82AD-B9041C6C7D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="139">
   <si>
     <t>HP 15</t>
   </si>
@@ -441,6 +441,21 @@
   <si>
     <t>s</t>
   </si>
+  <si>
+    <t>Don’t Offer Yet - For everyone's reference only</t>
+  </si>
+  <si>
+    <t>Maximum 20 units only until Oct 31, 2026</t>
+  </si>
+  <si>
+    <t>Maximum 10 units only until Oct 31, 2026</t>
+  </si>
+  <si>
+    <t>No Available Promo priced units as of Oct 13, 2026</t>
+  </si>
+  <si>
+    <t>Until Oct 31, 2026 Only</t>
+  </si>
 </sst>
 </file>
 
@@ -562,7 +577,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -608,6 +623,8 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -13483,20 +13500,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
   <dimension ref="B2:M41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.265625" customWidth="1"/>
+    <col min="13" max="13" width="38.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -13534,7 +13551,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
@@ -13568,7 +13585,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
@@ -13596,13 +13613,21 @@
         <f t="shared" ref="I4:I40" si="0">H4*0.85</f>
         <v>53541.5</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1">
+        <v>58990</v>
+      </c>
+      <c r="K4" s="17">
+        <f>J4*0.8</f>
+        <v>47192</v>
+      </c>
       <c r="L4" t="s">
         <v>65</v>
       </c>
+      <c r="M4" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
@@ -13636,7 +13661,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
@@ -13678,7 +13703,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
@@ -13716,11 +13741,11 @@
       <c r="L7" t="s">
         <v>65</v>
       </c>
-      <c r="M7" t="s">
-        <v>128</v>
+      <c r="M7" s="18" t="s">
+        <v>137</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
@@ -13762,7 +13787,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
@@ -13798,8 +13823,11 @@
       <c r="L9" t="s">
         <v>65</v>
       </c>
+      <c r="M9" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
@@ -13835,8 +13863,11 @@
       <c r="L10" t="s">
         <v>65</v>
       </c>
+      <c r="M10" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
@@ -13872,8 +13903,11 @@
       <c r="L11" t="s">
         <v>65</v>
       </c>
+      <c r="M11" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
@@ -13907,7 +13941,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
@@ -13941,7 +13975,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
@@ -13975,7 +14009,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
@@ -14009,7 +14043,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
@@ -14043,7 +14077,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
@@ -14077,7 +14111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
@@ -14111,7 +14145,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
@@ -14145,7 +14179,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
@@ -14179,7 +14213,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
@@ -14213,7 +14247,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
@@ -14247,7 +14281,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
@@ -14281,7 +14315,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>66</v>
       </c>
@@ -14308,12 +14342,21 @@
         <f t="shared" si="0"/>
         <v>55241.5</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1">
+        <v>44990</v>
+      </c>
+      <c r="K24" s="17">
+        <f>J24*0.8</f>
+        <v>35992</v>
+      </c>
       <c r="L24" t="s">
         <v>124</v>
       </c>
+      <c r="M24" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>67</v>
       </c>
@@ -14345,7 +14388,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
@@ -14372,12 +14415,21 @@
         <f t="shared" si="0"/>
         <v>56941.5</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1">
+        <v>56990</v>
+      </c>
+      <c r="K26" s="17">
+        <f>J26*0.8</f>
+        <v>45592</v>
+      </c>
       <c r="L26" t="s">
         <v>124</v>
       </c>
+      <c r="M26" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
@@ -14404,12 +14456,21 @@
         <f t="shared" si="0"/>
         <v>67141.5</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1">
+        <v>62990</v>
+      </c>
+      <c r="K27" s="17">
+        <f>J27*0.8</f>
+        <v>50392</v>
+      </c>
       <c r="L27" t="s">
         <v>124</v>
       </c>
+      <c r="M27" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B28" s="5" t="s">
         <v>70</v>
       </c>
@@ -14436,12 +14497,21 @@
         <f t="shared" si="0"/>
         <v>57791.5</v>
       </c>
-      <c r="J28" s="1"/>
+      <c r="J28" s="1">
+        <v>54990</v>
+      </c>
+      <c r="K28" s="17">
+        <f>J28*0.8</f>
+        <v>43992</v>
+      </c>
       <c r="L28" t="s">
         <v>124</v>
       </c>
+      <c r="M28" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>71</v>
       </c>
@@ -14473,7 +14543,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>72</v>
       </c>
@@ -14505,7 +14575,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>73</v>
       </c>
@@ -14537,7 +14607,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>74</v>
       </c>
@@ -14569,7 +14639,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>75</v>
       </c>
@@ -14601,7 +14671,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>76</v>
       </c>
@@ -14633,7 +14703,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
@@ -14665,7 +14735,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>78</v>
       </c>
@@ -14697,7 +14767,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>79</v>
       </c>
@@ -14729,7 +14799,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
@@ -14761,7 +14831,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>81</v>
       </c>
@@ -14793,7 +14863,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>82</v>
       </c>
@@ -14825,7 +14895,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B41" t="inlineStr">
         <is>
           <t>BQ5B1PT</t>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28D1CD0-2C76-4ADD-82AD-B9041C6C7D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D509AB6F-3D85-420C-BFE6-340537F306B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
@@ -577,7 +577,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -624,7 +624,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -13741,7 +13740,7 @@
       <c r="L7" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" t="s">
         <v>137</v>
       </c>
     </row>
@@ -14346,8 +14345,8 @@
         <v>44990</v>
       </c>
       <c r="K24" s="17">
-        <f>J24*0.8</f>
-        <v>35992</v>
+        <f>J24*0.85</f>
+        <v>38241.5</v>
       </c>
       <c r="L24" t="s">
         <v>124</v>
@@ -14419,8 +14418,8 @@
         <v>56990</v>
       </c>
       <c r="K26" s="17">
-        <f>J26*0.8</f>
-        <v>45592</v>
+        <f>J26*0.85</f>
+        <v>48441.5</v>
       </c>
       <c r="L26" t="s">
         <v>124</v>
@@ -14460,8 +14459,8 @@
         <v>62990</v>
       </c>
       <c r="K27" s="17">
-        <f>J27*0.8</f>
-        <v>50392</v>
+        <f>J27*0.85</f>
+        <v>53541.5</v>
       </c>
       <c r="L27" t="s">
         <v>124</v>
@@ -14501,8 +14500,8 @@
         <v>54990</v>
       </c>
       <c r="K28" s="17">
-        <f>J28*0.8</f>
-        <v>43992</v>
+        <f>J28*0.85</f>
+        <v>46741.5</v>
       </c>
       <c r="L28" t="s">
         <v>124</v>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D509AB6F-3D85-420C-BFE6-340537F306B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F340B75E-E2B5-4CE8-90A8-3B46B815BA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="140">
   <si>
     <t>HP 15</t>
   </si>
@@ -456,6 +456,9 @@
   <si>
     <t>Until Oct 31, 2026 Only</t>
   </si>
+  <si>
+    <t>40 units left only until Oct 31, 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -13699,7 +13702,7 @@
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.45">

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F340B75E-E2B5-4CE8-90A8-3B46B815BA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F186B0B0-6738-4CB2-9878-94884BE1C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
     <t>Until Oct 31, 2026 Only</t>
   </si>
   <si>
-    <t>40 units left only until Oct 31, 2026</t>
+    <t>20 units left only until Oct 31, 2026</t>
   </si>
 </sst>
 </file>
@@ -13502,20 +13502,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE742C-CFB6-4480-A0DE-B240110FF6C4}">
   <dimension ref="B2:M41"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.265625" customWidth="1"/>
-    <col min="13" max="13" width="38.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="str">
         <f>_xlfn.XLOOKUP(F3,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L5PA</v>
@@ -13587,7 +13587,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="str">
         <f>_xlfn.XLOOKUP(F4,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T8PA</v>
@@ -13629,7 +13629,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="str">
         <f>_xlfn.XLOOKUP(F5,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5U6PA</v>
@@ -13663,7 +13663,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="str">
         <f>_xlfn.XLOOKUP(F6,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U8PA</v>
@@ -13705,7 +13705,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="str">
         <f>_xlfn.XLOOKUP(F7,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW4U9PA</v>
@@ -13747,7 +13747,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="str">
         <f>_xlfn.XLOOKUP(F8,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW7W9PA</v>
@@ -13789,7 +13789,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>_xlfn.XLOOKUP(F9,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DJ8T4PA</v>
@@ -13829,7 +13829,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="str">
         <f>_xlfn.XLOOKUP(F10,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DX4J7PA</v>
@@ -13869,7 +13869,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="str">
         <f>_xlfn.XLOOKUP(F11,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5R6PA</v>
@@ -13909,7 +13909,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <f>_xlfn.XLOOKUP(F12,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S6PA</v>
@@ -13943,7 +13943,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <f>_xlfn.XLOOKUP(F13,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S7PA</v>
@@ -13977,7 +13977,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f>_xlfn.XLOOKUP(F14,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T2PA</v>
@@ -14011,7 +14011,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <f>_xlfn.XLOOKUP(F15,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S8PA</v>
@@ -14045,7 +14045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f>_xlfn.XLOOKUP(F16,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T6PA</v>
@@ -14079,7 +14079,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>_xlfn.XLOOKUP(F17,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S1PA</v>
@@ -14113,7 +14113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>_xlfn.XLOOKUP(F18,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S4PA</v>
@@ -14147,7 +14147,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f>_xlfn.XLOOKUP(F19,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5S5PA</v>
@@ -14181,7 +14181,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f>_xlfn.XLOOKUP(F20,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T4PA</v>
@@ -14215,7 +14215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" t="str">
         <f>_xlfn.XLOOKUP(F21,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DW8J8PA</v>
@@ -14249,7 +14249,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f>_xlfn.XLOOKUP(F22,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DU5T3PA</v>
@@ -14283,7 +14283,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f>_xlfn.XLOOKUP(F23,'[1]non-gaming'!$G:$G,'[1]non-gaming'!$D:$D)</f>
         <v>DM8L6PA</v>
@@ -14317,7 +14317,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>66</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>67</v>
       </c>
@@ -14390,7 +14390,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>70</v>
       </c>
@@ -14513,7 +14513,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>71</v>
       </c>
@@ -14545,7 +14545,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>72</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>73</v>
       </c>
@@ -14609,7 +14609,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>74</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>75</v>
       </c>
@@ -14673,7 +14673,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>76</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>78</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>79</v>
       </c>
@@ -14801,7 +14801,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
@@ -14833,7 +14833,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>81</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>82</v>
       </c>
@@ -14897,7 +14897,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" t="inlineStr">
         <is>
           <t>BQ5B1PT</t>

--- a/source/Current Pricelist - HPNB.xlsx
+++ b/source/Current Pricelist - HPNB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F186B0B0-6738-4CB2-9878-94884BE1C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AB0DE3-4EE5-4A21-A758-00A91DB9BCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{46EB8EAC-1B53-4337-BC93-2BB462C6E864}"/>
   </bookViews>
@@ -457,7 +457,7 @@
     <t>Until Oct 31, 2026 Only</t>
   </si>
   <si>
-    <t>20 units left only until Oct 31, 2026</t>
+    <t>10 units left only until Oct 31, 2026</t>
   </si>
 </sst>
 </file>
